--- a/Convert_from_xlsx_to_Json/table_normalization/education-table16.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table16.xlsx
@@ -653,7 +653,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,18 +740,33 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" textRotation="90"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection hidden="1"/>
@@ -764,45 +779,26 @@
       <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" textRotation="90"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" textRotation="90"/>
       <protection hidden="1"/>
     </xf>
@@ -1388,132 +1384,132 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="45">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
     </row>
     <row r="2" spans="1:18" ht="35">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
     </row>
     <row r="3" spans="1:18" ht="35">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="27" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="35"/>
-      <c r="F3" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="30" t="s">
+      <c r="E3" s="34"/>
+      <c r="F3" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="30" t="s">
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="31"/>
+      <c r="L3" s="26"/>
       <c r="M3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
       <c r="R3" s="36"/>
     </row>
     <row r="4" spans="1:18" ht="130">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="37" t="s">
+      <c r="C4" s="32"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="38" t="s">
+      <c r="F4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="39" t="s">
+      <c r="H4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="39" t="s">
+      <c r="L4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="39" t="s">
+      <c r="N4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="37" t="s">
+      <c r="O4" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="P4" s="39" t="s">
+      <c r="P4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="40" t="s">
+      <c r="Q4" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="R4" s="39" t="s">
+      <c r="R4" s="29" t="s">
         <v>14</v>
       </c>
     </row>
